--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92541003448</v>
+        <v>46157.93115410169</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115410169</v>
+        <v>46157.93368846997</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93368846997</v>
+        <v>46157.93673113597</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93673113597</v>
+        <v>46158.28195055737</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28195055737</v>
+        <v>46158.29719170306</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29719170306</v>
+        <v>46158.29791508786</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29791508786</v>
+        <v>46158.33356583677</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33356583677</v>
+        <v>46158.37211160873</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211160873</v>
+        <v>46158.37268122765</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
